--- a/countries/li/2020-2025.xlsx
+++ b/countries/li/2020-2025.xlsx
@@ -59681,17 +59681,17 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -59725,7 +59725,7 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LI_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -59750,7 +59750,7 @@
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LI_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT302" t="n">
@@ -59840,17 +59840,17 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -59876,12 +59876,12 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LI_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LI_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
@@ -59891,7 +59891,7 @@
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
@@ -59984,7 +59984,7 @@
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
+          <t>SER_LI_ECDC_HEPA_ANNUAL</t>
         </is>
       </c>
       <c r="AT303" t="n">
@@ -60074,17 +60074,17 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -60118,7 +60118,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -60143,7 +60143,7 @@
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT304" t="n">
@@ -60233,17 +60233,17 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>D040</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>风疹</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -60269,12 +60269,12 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
@@ -60284,7 +60284,7 @@
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>Rubella</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="Y305" t="inlineStr">
@@ -60377,7 +60377,7 @@
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+          <t>SER_LI_ECDC_MEAS_ANNUAL</t>
         </is>
       </c>
       <c r="AT305" t="n">
@@ -60467,17 +60467,17 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -60511,7 +60511,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LI_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -60536,7 +60536,7 @@
       </c>
       <c r="AS306" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LI_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT306" t="n">
@@ -60626,17 +60626,17 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D032</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>布鲁氏菌病</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -60662,12 +60662,12 @@
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LI_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LI_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="W307" t="inlineStr">
@@ -60677,7 +60677,7 @@
       </c>
       <c r="X307" t="inlineStr">
         <is>
-          <t>Legionnaires' disease</t>
+          <t>Brucellosis</t>
         </is>
       </c>
       <c r="Y307" t="inlineStr">
@@ -60770,7 +60770,7 @@
       </c>
       <c r="AS307" t="inlineStr">
         <is>
-          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+          <t>SER_LI_ECDC_BRUC_ANNUAL</t>
         </is>
       </c>
       <c r="AT307" t="n">
@@ -60817,6 +60817,3150 @@
         </is>
       </c>
       <c r="BC307" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP308" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV308" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA308" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB308" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC308" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>D040</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>风疹</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Rubella</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP309" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_RUBE_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV309" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX309" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY309" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA309" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB309" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC309" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>40</v>
+      </c>
+      <c r="O310" t="n">
+        <v>40</v>
+      </c>
+      <c r="R310" t="n">
+        <v>99.6810207336523</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO310" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP310" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ310" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU310" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV310" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW310" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX310" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY310" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA310" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB310" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC310" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N311" t="n">
+        <v>40</v>
+      </c>
+      <c r="O311" t="n">
+        <v>40</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA311" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN311" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO311" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP311" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ311" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS311" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_CAMP_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU311" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV311" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW311" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX311" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY311" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA311" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB311" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC311" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU312" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV312" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW312" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX312" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY312" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA312" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB312" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC312" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN313" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SHIG_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV314" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW314" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX314" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY314" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA314" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB314" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC314" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Legionellosis</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>军团菌病</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Legionnaires' disease</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LEGI_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_LIST_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>10</v>
+      </c>
+      <c r="O318" t="n">
+        <v>10</v>
+      </c>
+      <c r="R318" t="n">
+        <v>24.92025518341308</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>10</v>
+      </c>
+      <c r="O319" t="n">
+        <v>10</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_SALM_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N320" t="n">
+        <v>6</v>
+      </c>
+      <c r="O320" t="n">
+        <v>6</v>
+      </c>
+      <c r="R320" t="n">
+        <v>14.95215311004785</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>6</v>
+      </c>
+      <c r="O321" t="n">
+        <v>6</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>STEC/VTEC infection</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN321" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_STEC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU321" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV321" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW321" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA321" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB321" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC321" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>0</v>
+      </c>
+      <c r="O322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>li</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Liechtenstein</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D122</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>旋毛虫病</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>0</v>
+      </c>
+      <c r="O323" t="n">
+        <v>0</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>SRC_LI_ECDC_ATLAS</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>Trichinellosis</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>ecdc_member_state_reported_aggregate_surveillance</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>country:LI:national</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>ECDC_CURRENT_GENERAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>Liechtenstein annual Member-State reported aggregate cases from the public ECDC Surveillance Atlas; published zeroes are explicit, absent topic/year cells remain unknown, and combined populations are emitted only when every reviewed component is present. Data provided by ECDC based on data reported by EU/EEA Member States.</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN323" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_LI_ECDC_TRIC_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AT323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>official_ecdc_rest_aggregate</t>
+        </is>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>ecdc_atlas_annual</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr">
+        <is>
+          <t>ECDC Surveillance Atlas — Liechtenstein Annual Baseline</t>
+        </is>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>https://atlas.ecdc.europa.eu/public/index.aspx/</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr">
         <is>
           <t>official_ecdc_rest_aggregate</t>
         </is>
@@ -60938,7 +64082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10">
@@ -60948,7 +64092,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>306</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -60968,7 +64112,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -61000,7 +64144,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>539</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16">
